--- a/public/exports-60-250/29189935.xlsx
+++ b/public/exports-60-250/29189935.xlsx
@@ -5614,7 +5614,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t xml:space="preserve">200025503</t>
+          <t xml:space="preserve">200025497</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
